--- a/DataDump/Data_Graphs.xlsx
+++ b/DataDump/Data_Graphs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MAS\PycharmProjects\MA-Metier_P14_Autopilot_RC\DataDump\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pt52obq\PycharmProjects\MA-Metier_P14_Autopilot_RC\DataDump\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FE997C-4E91-4211-B196-9F0637AE0A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02907A8-B964-43F5-9B26-0C553AB109E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{287B0832-DEEC-4041-9F75-8ACA47D10402}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="700" xr2:uid="{287B0832-DEEC-4041-9F75-8ACA47D10402}"/>
   </bookViews>
   <sheets>
     <sheet name="Datas" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Chemin du planeur" sheetId="11" r:id="rId3"/>
     <sheet name="Vitesse du planeur" sheetId="12" r:id="rId4"/>
     <sheet name="Rapport vit. verticale et alt." sheetId="13" r:id="rId5"/>
+    <sheet name="Inclinaison du planeur" sheetId="14" r:id="rId6"/>
+    <sheet name="Tangage du planeur" sheetId="15" r:id="rId7"/>
+    <sheet name="Variomètre" sheetId="16" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="DonnéesExternes_1" localSheetId="0" hidden="1">Datas!$A$1:$T$12</definedName>
@@ -196,11 +199,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -228,11 +230,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -247,8 +248,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -257,24 +258,31 @@
             <c:v>Altitude du planeur</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:trendline>
             <c:spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln w="25400" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:prstDash val="sysDot"/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -282,7 +290,7 @@
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Datas!$E$2:$E$12</c:f>
               <c:numCache>
@@ -323,8 +331,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-94FA-4757-A6B0-EDC0BF4BEEBE}"/>
@@ -338,18 +346,24 @@
             <c:v>Altitude du sol</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent3">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Datas!$G$2:$G$12</c:f>
               <c:numCache>
@@ -390,8 +404,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-94FA-4757-A6B0-EDC0BF4BEEBE}"/>
@@ -406,28 +420,66 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="617652799"/>
         <c:axId val="617653279"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="617652799"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="617653279"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="617653279"/>
         <c:scaling>
@@ -439,9 +491,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -455,8 +508,13 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -467,9 +525,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -482,7 +539,7 @@
         </c:txPr>
         <c:crossAx val="617652799"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -493,7 +550,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -509,9 +566,8 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -536,11 +592,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -590,11 +649,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -619,24 +677,31 @@
             <c:v>Chemin du planeur</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:trendline>
             <c:spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln w="25400" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:prstDash val="sysDot"/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -646,6 +711,48 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
+              <c:f>Datas!$D$2:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>11.5558</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.5557</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.555400000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.555099999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.555</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.555999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.5585</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.5623</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.5655</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.5665</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.563800000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
               <c:f>Datas!$C$2:$C$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
@@ -682,48 +789,6 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>43.501600000000003</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datas!$D$2:$D$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>11.5558</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>11.5557</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>11.555400000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>11.555099999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>11.555</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>11.555999999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>11.5585</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>11.5623</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>11.5655</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>11.5665</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11.563800000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -757,9 +822,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -775,9 +841,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -791,9 +856,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -819,9 +883,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -837,9 +902,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -853,9 +917,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -878,6 +941,36 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -891,11 +984,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -938,11 +1034,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -952,13 +1047,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="fr-CH"/>
-              <a:t>Vitesses</a:t>
+              <a:t>Vitesses du planeur</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="fr-CH" baseline="0"/>
-              <a:t> du planeur</a:t>
-            </a:r>
-            <a:endParaRPr lang="fr-CH"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -975,11 +1065,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -994,8 +1083,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1004,18 +1093,24 @@
             <c:v>Vitesse Indiquée</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Datas!$H$2:$H$12</c:f>
               <c:numCache>
@@ -1056,8 +1151,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-E41A-4D0C-9178-BF7D925C3B52}"/>
@@ -1071,18 +1166,24 @@
             <c:v>Vitesse au dessus du sol</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Datas!$I$2:$I$12</c:f>
               <c:numCache>
@@ -1123,8 +1224,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-E41A-4D0C-9178-BF7D925C3B52}"/>
@@ -1139,17 +1240,31 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="589158479"/>
         <c:axId val="589158959"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="589158479"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1157,10 +1272,66 @@
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="589158959"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="589158959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1174,68 +1345,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="589158959"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="589158959"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1248,7 +1359,7 @@
         </c:txPr>
         <c:crossAx val="589158479"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1259,7 +1370,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1275,9 +1386,8 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1302,11 +1412,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -1349,11 +1462,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1363,7 +1475,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="fr-CH"/>
-              <a:t>Rapport vitesse vertical et altitude</a:t>
+              <a:t>Rapport vitesse verticale et altitude</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1381,11 +1493,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1400,8 +1511,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1410,18 +1521,24 @@
             <c:v>Altitude du planeur</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Datas!$E$2:$E$12</c:f>
               <c:numCache>
@@ -1462,30 +1579,14 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-C7C8-481C-A4A7-2057C45342F1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="328575935"/>
-        <c:axId val="328587935"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -1493,18 +1594,24 @@
             <c:v>vitesse vertical</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Datas!$J$2:$J$12</c:f>
               <c:numCache>
@@ -1545,8 +1652,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-C7C8-481C-A4A7-2057C45342F1}"/>
@@ -1561,29 +1668,66 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="408964255"/>
-        <c:axId val="408958495"/>
-      </c:lineChart>
-      <c:catAx>
+        <c:axId val="328575935"/>
+        <c:axId val="328587935"/>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="328575935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="328587935"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="328587935"/>
         <c:scaling>
@@ -1595,9 +1739,793 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="328575935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CH"/>
+              <a:t>Inclinaison du planeur</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Inclinaison</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datas!$K$2:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-0.77739999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.34160000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.18790000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.8883999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12.1221</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.162600000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.322100000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.050799999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.7203999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.2488000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E7CD-4FC7-A46C-476BF7B7585C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1511001488"/>
+        <c:axId val="1511003888"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1511001488"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1511003888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1511003888"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1511001488"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CH"/>
+              <a:t>Tangage du planeur</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Tangage</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>Datas!$L$2:$L$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2.7334999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.3235000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7444</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5.2549999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-21.429600000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-33.8371</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-39.5914</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-41.971600000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-41.996699999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-40.3979</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18.9206</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-64CD-42CC-8EDD-C2B3BDDB991E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="1699071696"/>
+        <c:axId val="1726475088"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1699071696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1726475088"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1726475088"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1623,9 +2551,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1636,72 +2563,10 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="328575935"/>
+        <c:crossAx val="1699071696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="408958495"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="10000"/>
-          <c:min val="-6000"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="r"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="408964255"/>
-        <c:crosses val="max"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:catAx>
-        <c:axId val="408964255"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="408958495"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1711,7 +2576,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1727,9 +2592,389 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CH"/>
+              <a:t>Variomètre</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Variomètre</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datas!$N$2:$N$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-3.5501999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.8209</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-6.1750999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.3597000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-11.573399999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-33.207799999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-53.0702</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-55.554200000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-83.392399999999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-48.562199999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-6.7107000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4708-4CED-B3AC-FB27CDA92B09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="379861408"/>
+        <c:axId val="379858048"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="379861408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="379858048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="379858048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="379861408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1754,11 +2999,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -1940,728 +3188,156 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -2672,78 +3348,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -2751,295 +3356,15 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="lt1">
         <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3049,23 +3374,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -3073,84 +3393,131 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:effectRef idx="0">
       <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
-      </a:ln>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="phClr"/>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -3166,21 +3533,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3190,7 +3554,368 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -3199,389 +3924,6 @@
           <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -3589,84 +3931,131 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:effectRef idx="0">
       <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
-      </a:ln>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="phClr"/>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -3682,21 +4071,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3706,7 +4092,368 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -3715,17 +4462,258 @@
           <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -3735,80 +4723,10 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3820,14 +4738,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3839,14 +4756,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3858,27 +4774,26 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -3886,9 +4801,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3898,14 +4812,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3917,12 +4830,11 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -3931,14 +4843,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3947,11 +4860,1595 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
@@ -3959,7 +6456,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -3967,9 +6464,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -3980,9 +6477,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3994,12 +6490,544 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -4037,11 +7065,35 @@
 </chartsheet>
 </file>
 
+<file path=xl/chartsheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{4725EBF5-594D-408E-8186-125D3C5D1881}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{FFF3193D-2EEE-409E-BB07-19A959F1BB84}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{042BBBAE-7CFC-40D4-B5FA-710D0EAEB22D}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9288910" cy="6048782"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Graphique 1">
@@ -4074,7 +7126,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9288910" cy="6048782"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Graphique 1">
@@ -4107,7 +7159,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9288910" cy="6048782"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Graphique 1">
@@ -4140,13 +7192,112 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9288910" cy="6048782"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95BF2AC-F3E0-6990-A95F-A1F38C1DD33C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9288910" cy="6048782"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E181E27B-06E0-A562-1E42-DD20764E2F6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9288910" cy="6048782"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F6F4DD6-DC4D-DF7F-787B-3F0A19758D1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9280769" cy="6056923"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C482088-D19B-B812-B309-B23037CB3C34}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
